--- a/sources/gunjack_step8.xlsx
+++ b/sources/gunjack_step8.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB119"/>
+  <dimension ref="A1:AB121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -4405,12 +4405,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>db+1,1,1,[1,1],2</t>
+          <t>db+1,1,1,2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>db+1,1,1,[1,1],2</t>
+          <t>db+1,1,1,2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4435,669 +4435,629 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -18</t>
+          <t>-6 -6 -11 -18</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-6 -6 -6 -6 -11 -18</t>
+          <t>-6 -6 -11 -18</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>+5 +5 +5 +5 0 KD</t>
+          <t>+5 +5 0 KD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>15,15,15,15,15,40</t>
+          <t>15,15,15,40</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15,15,15,15,15,40</t>
+          <t>15,15,15,40</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>lllllm</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>lllllm</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>ab11e12d-c483-4b93-9879-06d76d1fca71</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>568bdad4-12b5-4f8f-a34d-d39e8eff9bc3</t>
+          <t>3dfc05af-5516-438c-9613-534804a1c3bb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1,1,1,1,2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>b,db,d,DF+1</t>
+          <t>db+1,1,1,1,2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Debugger</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -18</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-6 -6 -6 -11 -18</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15,15,15,15,40</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15,15,15,15,40</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>llllm</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>0b8ca525-62ed-4ff3-8dc7-149b3e406b6a</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>c1b0d6be-6746-4b38-b003-4c326fe47393</t>
+          <t>cb9ca34f-2dcd-4444-bb8a-409bc1f3ce79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hcf+1</t>
+          <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hcf+1</t>
+          <t>db+1,1,1,1,1,2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gigaton Punch</t>
+          <t>Machine Gun - Megaton Punch</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-6 -6 -6 -6 -11 -18</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>-6 -6 -6 -6 -11 -18</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 +5 +5 +5 0 KD</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15,15,15,15,15,40</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15,15,15,15,15,40</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>lllllm</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>c63c3f24-d4bd-477f-88ec-1f02a282278d</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>3c395486-f2d9-4b0a-8465-411361b774e0</t>
+          <t>3fc4e6c7-b2f3-4a63-944b-235077793821</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DF+1,2,1,2</t>
+          <t>b,db,d,DF+1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Uppercut Rush</t>
+          <t>Debugger</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-11 -7 -9 -2</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0 +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0 +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0 +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0 +4 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>10,15,10,15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Will only juggles if the first hit connected as a counter hit.</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>ecd54e05-ddf1-400b-996e-bdefca3d94e7</t>
+          <t>0b8ca525-62ed-4ff3-8dc7-149b3e406b6a</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>7fae9dc9-a263-4ffe-83cf-6196cf208723</t>
+          <t>c1b0d6be-6746-4b38-b003-4c326fe47393</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>hcf+1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2,1</t>
+          <t>hcf+1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Gigaton Punch</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>Gigaton Punch</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-6 -8 -2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>+5 +2 +9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Will only juggles if the first hit connected as a counter hit.</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>d333eb59-e1a6-4f76-a14c-44169352ace9</t>
+          <t>c63c3f24-d4bd-477f-88ec-1f02a282278d</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>3ef88e6f-07e4-4bc3-9d38-d88a71051a4f</t>
+          <t>3c395486-f2d9-4b0a-8465-411361b774e0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>hcf,DF+1</t>
+          <t>DF+1,2,1,2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Megaton Uppercut</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Megaton Uppercut</t>
+          <t>Uppercut Rush</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-11 -7 -9 -2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>0 +4 +2 +9</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>0 +4 +2 +9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>0 +4 +2 +9</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>0 +4 +2 +9</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,10,15</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Will only juggles if the first hit connected as a counter hit.</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>9bfafeb9-c3d0-45ce-bdec-76847964099d</t>
+          <t>ecd54e05-ddf1-400b-996e-bdefca3d94e7</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>91944806-d22f-461f-b205-74941873d01d</t>
+          <t>7fae9dc9-a263-4ffe-83cf-6196cf208723</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>Df+1,2,1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1</t>
+          <t>Df+1,2,1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2,1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Windmill</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>-22 -22 -2</t>
+          <t>-6 -8 -2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-12 -12 -12</t>
+          <t>+5 +2 +9</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12,15,15</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5107,7 +5067,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>12,15,15</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5120,36 +5080,51 @@
           <t>mmm</t>
         </is>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Will only juggles if the first hit connected as a counter hit.</t>
+        </is>
+      </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>3b640b0c-7033-4bcd-b4db-99afbfe6d511</t>
+          <t>d333eb59-e1a6-4f76-a14c-44169352ace9</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>7cb2fdb1-3f59-434f-a09a-f8b9418d72f3</t>
+          <t>3ef88e6f-07e4-4bc3-9d38-d88a71051a4f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>hcf,DF+1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FC+df+1,2,1,1</t>
+          <t>hcf,DF+1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>– Windmill Backhand</t>
+          <t>Megaton Uppercut</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Windmill – Windmill Backhand</t>
+          <t>Megaton Uppercut</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5159,12 +5134,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>-22 -22 -2 +20</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5174,7 +5149,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5184,278 +5159,283 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>-12 -12 -12 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>12,15,15,30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>mmmh</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>CF GB</t>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>122be798-30de-4a56-9cf3-8f3e6feb3d0a</t>
+          <t>9bfafeb9-c3d0-45ce-bdec-76847964099d</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>374f7127-7acf-4106-b06b-9f0004186719</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>3b640b0c-7033-4bcd-b4db-99afbfe6d511</t>
+          <t>91944806-d22f-461f-b205-74941873d01d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>FC+DF+1,2</t>
+          <t>FC+df+1,2,1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Medium Uppercut Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Medium Uppercut Rush</t>
+          <t>Windmill</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>-6 -8</t>
+          <t>-22 -22 -2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>+5 +2</t>
+          <t>-12 -12 -12</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>12,15,15</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>12,15,15</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
+          <t>3b640b0c-7033-4bcd-b4db-99afbfe6d511</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>3486eb95-9b40-461b-9821-1987f0069555</t>
+          <t>7cb2fdb1-3f59-434f-a09a-f8b9418d72f3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Df+1,2,d+1</t>
+          <t>FC+df+1,2,1,1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>– Windmill Backhand</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Medium Uppercut Rush – Low Punch</t>
+          <t>Windmill – Windmill Backhand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>-6 -8 -17</t>
+          <t>-22 -22 -2 +20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>+5 +2 -7</t>
+          <t>-12 -12 -12 KD</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>15,12,8</t>
+          <t>12,15,15,30</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>mmL</t>
+          <t>mmmh</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CF GB</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>e7231930-e59a-43fc-bf5a-66fa199c9517</t>
+          <t>122be798-30de-4a56-9cf3-8f3e6feb3d0a</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>fd052b97-6b23-409d-8c12-ffc90fdeb445</t>
+          <t>374f7127-7acf-4106-b06b-9f0004186719</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
+          <t>3b640b0c-7033-4bcd-b4db-99afbfe6d511</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+1,2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Df+1,2,df+1</t>
+          <t>Df+1,2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FC+DF+1,2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Medium Uppercut Rush</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Medium Uppercut Rush – Mid Punch</t>
+          <t>Medium Uppercut Rush</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5465,99 +5445,89 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>-6 -8 -1</t>
+          <t>-6 -8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>+5 +2 +10</t>
+          <t>+5 +2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>15,12,15</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>261af1fe-01d4-41d5-8019-73b2cb65e56d</t>
+          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>dea01a89-fc08-4369-a34f-96d7be0a235e</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
+          <t>3486eb95-9b40-461b-9821-1987f0069555</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Df+1,2,f+1</t>
+          <t>Df+1,2,d+1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Medium Uppercut Rush – High Punch</t>
+          <t>Medium Uppercut Rush – Low Punch</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5577,57 +5547,62 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>+5 +2 -5</t>
+          <t>+5 +2 -7</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>15,12,12</t>
+          <t>15,12,8</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>mmh</t>
+          <t>mmL</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>bed70df3-90e1-4204-b0e9-4177c42ca0fc</t>
+          <t>e7231930-e59a-43fc-bf5a-66fa199c9517</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>8332d3e8-a2b0-46a9-baac-ea7e14739587</t>
+          <t>fd052b97-6b23-409d-8c12-ffc90fdeb445</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -5639,87 +5614,82 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FC+db+1,1,1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FC+db+1,1,1,2</t>
+          <t>Df+1,2,df+1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Revolving Knuckles - Megaton</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Revolving Knuckles - Megaton</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>Medium Uppercut Rush – Mid Punch</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-1 +1 +1 -20</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>-1 +1 +1 -20</t>
+          <t>-6 -8 -1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>+10 +12 +12 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>+10 +12 +12 KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+10 +12 +12 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>+10 +12 +12 KD</t>
+          <t>+5 +2 +10</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>18,25,25,40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>18,25,25,40</t>
+          <t>15,12,15</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>lllm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>lllm</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -5729,196 +5699,201 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>d113b86c-a1fe-411e-a6e3-b3bf57a5a99e</t>
+          <t>261af1fe-01d4-41d5-8019-73b2cb65e56d</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>2077988b-4b16-4735-b162-ddd746e9cb3d</t>
+          <t>dea01a89-fc08-4369-a34f-96d7be0a235e</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2</t>
+          <t>Df+1,2,f+1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hammer Rush</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>Medium Uppercut Rush – High Punch</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8</t>
+          <t>-6 -8 -17</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1</t>
+          <t>+5 +2 -5</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>10,8,12,12</t>
+          <t>15,12,12</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>LLmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>LLmm</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
+          <t>bed70df3-90e1-4204-b0e9-4177c42ca0fc</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>8d43be6c-1290-4ebb-ba82-aa1aefbb561b</t>
+          <t>8332d3e8-a2b0-46a9-baac-ea7e14739587</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>6f1a5741-eeb3-406f-a85f-72ccfc539ef1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>FC+db+1,1,1,2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,d+1</t>
+          <t>FC+db+1,1,1,2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Revolving Knuckles - Megaton</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hammer Rush – Low Punch</t>
+          <t>Revolving Knuckles - Megaton</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-1 +1 +1 -20</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -17</t>
+          <t>-1 +1 +1 -20</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+10 +12 +12 KD</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 -7</t>
+          <t>+10 +12 +12 KD</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+10 +12 +12 KD</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 -7</t>
+          <t>+10 +12 +12 KD</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18,25,25,40</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>10,8,12,12,8</t>
+          <t>18,25,25,40</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>LLmmL</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -5928,39 +5903,39 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>ee1a8afc-44ad-458b-90b6-66ab58357b26</t>
+          <t>d113b86c-a1fe-411e-a6e3-b3bf57a5a99e</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>ddf6bd1e-552d-469f-943d-b041e19298ad</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
+          <t>2077988b-4b16-4735-b162-ddd746e9cb3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,df+1</t>
+          <t>FC+1,1,1,2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Hammer Rush</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hammer Rush – Mid Punch</t>
+          <t>Hammer Rush</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5970,57 +5945,57 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-8 +1 -12 -8 -1</t>
+          <t>-8 +1 -12 -8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -2 +1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 +10</t>
+          <t>+2 +12 -2 +1</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+2 +12 -2 +1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 +10</t>
+          <t>+2 +12 -2 +1</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>10,8,12,12,15</t>
+          <t>10,8,12,12</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>LLmmm</t>
+          <t>LLmm</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6030,39 +6005,34 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>4f1ca9f4-80e6-4096-a3eb-49fb9fb01624</t>
+          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>c9f9f421-4e79-4f10-8989-ccef7d1a3b03</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
+          <t>8d43be6c-1290-4ebb-ba82-aa1aefbb561b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FC+1,1,1,2,f+1</t>
+          <t>FC+1,1,1,2,d+1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hammer Rush – High Punch</t>
+          <t>Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6082,57 +6052,62 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 -5</t>
+          <t>+2 +12 -2 +1 -7</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>+2 +12 -2 +1 -5</t>
+          <t>+2 +12 -2 +1 -7</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>10,8,12,12,12</t>
+          <t>10,8,12,12,8</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>LLmmh</t>
+          <t>LLmmL</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>f9f637a3-ee37-4f89-b10f-15e0c8382e99</t>
+          <t>ee1a8afc-44ad-458b-90b6-66ab58357b26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>dc7d0b74-0571-4444-8832-418fe814b31f</t>
+          <t>ddf6bd1e-552d-469f-943d-b041e19298ad</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -6144,87 +6119,82 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FC+1,2</t>
+          <t>FC+1,1,1,2,df+1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Low Punch - Megaton Punch</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+          <t>Hammer Rush – Mid Punch</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-8 -14</t>
+          <t>-8 +1 -12 -8 -1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -2 +1 +10</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>+2 KD</t>
+          <t>+2 +12 -2 +1 +10</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>10,8,12,12,15</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>LLmmm</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -6234,243 +6204,238 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>8d02ac25-44bc-45ea-b4ff-d8ffb35d80ce</t>
+          <t>4f1ca9f4-80e6-4096-a3eb-49fb9fb01624</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>05d6c665-49ed-484d-b2a2-04b45277976d</t>
+          <t>c9f9f421-4e79-4f10-8989-ccef7d1a3b03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1+2&lt;1+2</t>
+          <t>FC+1,1,1,2,f+1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hammer Knuckle - Double Uppercut</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Hammer Rush – High Punch</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-15 -22</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-15 -22</t>
+          <t>-8 +1 -12 -8 -17</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -2 +1 -5</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 +12 -2 +1 -5</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>21,22</t>
+          <t>10,8,12,12,12</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>LLmmh</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>8d0d6d15-919d-4c1c-8ccb-2a66cd1c6132</t>
+          <t>f9f637a3-ee37-4f89-b10f-15e0c8382e99</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>7e052b30-6e75-470b-959c-55c163a18ec4</t>
+          <t>dc7d0b74-0571-4444-8832-418fe814b31f</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>96cba551-37e1-4dc3-a68e-5c7cbc41979c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WS+1+2&lt;1+2</t>
+          <t>FC+1,2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Double Uppercut - Hammer Knuckle</t>
+          <t>Low Punch - Megaton Punch</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-16 -15</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-16 -15</t>
+          <t>-8 -14</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>+2 KD</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>21,17</t>
+          <t>10,25</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>50344c1a-8ea6-40a8-b948-419c27ffd3a4</t>
+          <t>8d02ac25-44bc-45ea-b4ff-d8ffb35d80ce</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>913c3051-5e5c-4776-ac4b-562b88ceed12</t>
+          <t>05d6c665-49ed-484d-b2a2-04b45277976d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F+1+2</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>F+1+2</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>f+1+2</t>
+          <t>1+2&lt;1+2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Arm Scissors</t>
+          <t>Hammer Knuckle - Double Uppercut</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6485,109 +6450,119 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -22</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -22</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,22</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
+          <t>8d0d6d15-919d-4c1c-8ccb-2a66cd1c6132</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>311e1b17-975d-4e36-9cff-f93c2c288c41</t>
+          <t>7e052b30-6e75-470b-959c-55c163a18ec4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>– 1+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>F+1+2,1+2</t>
+          <t>WS+1+2&lt;1+2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>– Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Arm Scissors – Cross Cut Saw</t>
+          <t>Double Uppercut - Hammer Knuckle</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-16 -15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-10 -19</t>
+          <t>-16 -15</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6597,7 +6572,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6607,69 +6582,74 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>aac36883-1144-4e6b-a435-0246703d2cef</t>
+          <t>50344c1a-8ea6-40a8-b948-419c27ffd3a4</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>1e566dc2-c682-4cbe-915d-49dd815f7e2f</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
+          <t>913c3051-5e5c-4776-ac4b-562b88ceed12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>– ~df+2</t>
+          <t>F+1+2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>F+1+2~df+2</t>
+          <t>F+1+2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>– Megaton Punch</t>
+          <t>Arm Scissors</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arm Scissors – Megaton Punch</t>
+          <t>Arm Scissors</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6679,12 +6659,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-10 -14</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6694,7 +6674,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6704,22 +6684,22 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -6729,69 +6709,54 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>950f989f-16db-48a4-a69a-1429e6676061</t>
+          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>1bced89b-175d-493e-ad3c-581aadc1582b</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
+          <t>311e1b17-975d-4e36-9cff-f93c2c288c41</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>– 1+2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>d+1+2</t>
+          <t>F+1+2,1+2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
+          <t>– Cross Cut Saw</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bravo Knuckle</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Arm Scissors – Cross Cut Saw</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-10 -19</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6801,7 +6766,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6811,99 +6776,89 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>17,15</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>3c5514df-ee77-403e-a02e-d3b0ec11068f</t>
+          <t>aac36883-1144-4e6b-a435-0246703d2cef</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>6d5c492f-91df-439b-a868-143688470c0c</t>
+          <t>1e566dc2-c682-4cbe-915d-49dd815f7e2f</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>– ~df+2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FC+1+2</t>
+          <t>F+1+2~df+2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Low Palm Lift</t>
+          <t>– Megaton Punch</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Low Palm Lift</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>23</t>
+          <t>Arm Scissors – Megaton Punch</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-10 -14</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6913,7 +6868,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6923,94 +6878,94 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>GB RC</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>b3dd1923-0530-4ecb-bf98-7949946f1a0a</t>
+          <t>950f989f-16db-48a4-a69a-1429e6676061</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>87bf032a-dfdb-4bc9-92a4-05b8e9025323</t>
+          <t>1bced89b-175d-493e-ad3c-581aadc1582b</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>16cb5524-5d2b-431e-80de-0ae348d0a036</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FC+df+1+2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FC+df+1+2</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Df+1+2</t>
+          <t>d+1+2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cross Cut Saw</t>
+          <t>Bravo Knuckle</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7035,390 +6990,395 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG GB</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>When tagging in Bryan Fury hit 2 to grab the opponent in mid air and do a Fisherman's Slam. Total damage is 21,21.</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>a17b0e2c-dcbf-4dad-8e8c-49d9525d1a2f</t>
+          <t>3c5514df-ee77-403e-a02e-d3b0ec11068f</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>a8511eeb-a807-44a3-9f06-bc5d8767f7b6</t>
+          <t>6d5c492f-91df-439b-a868-143688470c0c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>b+1+2</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>b+1+2</t>
+          <t>FC+1+2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Piston Gun</t>
+          <t>Low Palm Lift</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Piston Gun</t>
+          <t>Low Palm Lift</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20 x x x x</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>20 x x x x</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>x x x x +1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>x x x x +1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>x x x x KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>x x x x KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>x x x x KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>x x x x KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>7,5,5,5,21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>7,5,5,5,21</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>hhhhh</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>hhhhh</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>GB RC</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>cb0adf6a-4936-4311-a5bb-c659d630affc</t>
+          <t>b3dd1923-0530-4ecb-bf98-7949946f1a0a</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>881f4b35-f8be-426a-8b14-8a19f03308b8</t>
+          <t>87bf032a-dfdb-4bc9-92a4-05b8e9025323</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>df+1+3</t>
+          <t>FC+df+1+2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>df+1+3</t>
+          <t>FC+df+1+2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Df+1+2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Body Press</t>
+          <t>Cross Cut Saw</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Body Press</t>
+          <t>Cross Cut Saw</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-19</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-19</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Throws on a hit in close range, damage will be 25 on a throw. Causes Guard Break on a block.</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>235a1a3c-fc63-4355-94c5-deb559a7b211</t>
+          <t>a17b0e2c-dcbf-4dad-8e8c-49d9525d1a2f</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>1880b58e-dd1c-45a0-90ca-ea16bac535aa</t>
+          <t>a8511eeb-a807-44a3-9f06-bc5d8767f7b6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2,1,2</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Piston Gun</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Punch - Elbow - Uppercut</t>
+          <t>Piston Gun</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20 x x x x</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20 x x x x</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>x x x x +1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0 0 -15</t>
+          <t>x x x x +1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>x x x x KD</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>x x x x KD</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>x x x x KD</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>+7 +2 KD</t>
+          <t>x x x x KD</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>7,5,5,5,21</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>12,15,20</t>
+          <t>7,5,5,5,21</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>hhhhh</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>hmm</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>JG RC</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>hhhhh</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>9facfeeb-611f-4321-b9ce-e8602fb6721f</t>
+          <t>cb0adf6a-4936-4311-a5bb-c659d630affc</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>b23b21ed-b733-42ba-88c9-2cc296cb4c7b</t>
+          <t>881f4b35-f8be-426a-8b14-8a19f03308b8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>df+1+3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Df+2</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>FC+df+2</t>
+          <t>df+1+3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
+          <t>Body Press</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Short Hammer Rush</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>-2</t>
+          <t>Body Press</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7431,143 +7391,158 @@
           <t>m</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>RC</t>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Throws on a hit in close range, damage will be 25 on a throw. Causes Guard Break on a block.</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
+          <t>235a1a3c-fc63-4355-94c5-deb559a7b211</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>814da5c3-b433-4dd5-b13b-0ccd63f85b89</t>
+          <t>1880b58e-dd1c-45a0-90ca-ea16bac535aa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>– d+1</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Df+2,d+1</t>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>– Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Low Punch</t>
+          <t>Punch - Elbow - Uppercut</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>-13 -17</t>
+          <t>0 0 -15</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-2 -7</t>
+          <t>+7 +2 KD</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>10,8</t>
+          <t>12,15,20</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG RC</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>a9afcf8d-4b09-4d05-9be9-7b77179dd22b</t>
+          <t>9facfeeb-611f-4321-b9ce-e8602fb6721f</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>e056bdf1-9d30-44c5-b239-d939aa3df7d6</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
+          <t>b23b21ed-b733-42ba-88c9-2cc296cb4c7b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>– df+1</t>
+          <t>Df+2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Df+2,df+1</t>
+          <t>Df+2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>– Mid Punch</t>
+          <t>Short Hammer Rush</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – Mid Punch</t>
+          <t>Short Hammer Rush</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7577,47 +7552,47 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>-13 -1</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>-2 +10</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -7627,7 +7602,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -7637,39 +7612,34 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>dcf158c2-3b69-4965-bf0c-cfc2ed3c2b7b</t>
+          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>006e1dd1-451f-4b5f-be3e-1593d8b1dba2</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
+          <t>814da5c3-b433-4dd5-b13b-0ccd63f85b89</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>– f+1</t>
+          <t>– d+1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Df+2,f+1</t>
+          <t>Df+2,d+1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>– High Punch</t>
+          <t>– Low Punch</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Short Hammer Rush – High Punch</t>
+          <t>Short Hammer Rush – Low Punch</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7689,57 +7659,62 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-2 -5</t>
+          <t>-2 -7</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>ed27d523-e067-478d-a635-03bda68904ba</t>
+          <t>a9afcf8d-4b09-4d05-9be9-7b77179dd22b</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>44d5340f-99e1-4aac-9e14-e98997b4543e</t>
+          <t>e056bdf1-9d30-44c5-b239-d939aa3df7d6</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -7751,455 +7726,455 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>– df+1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DF+2,1,2,1</t>
+          <t>Df+2,df+1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
+          <t>– Mid Punch</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hammer Uppercut Rush</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+          <t>Short Hammer Rush – Mid Punch</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-13 -1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-2 +10</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>-2 +10</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-11 -6 -9 -1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-11 -6 -9 -1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>KD +5 +3 +10</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>KD +5 +3 +10</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>KD +5 +3 +10</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>KD +5 +3 +10</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>10,15,12,15</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>10,15,12,15</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>mmmm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>eb0be9ab-e619-4f81-9092-4a7389c2ce1f</t>
+          <t>dcf158c2-3b69-4965-bf0c-cfc2ed3c2b7b</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>9438c263-e8fc-4e2c-af89-31a54e2587cc</t>
+          <t>006e1dd1-451f-4b5f-be3e-1593d8b1dba2</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>– f+1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>FC+DF+2,1,2</t>
+          <t>Df+2,f+1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
+          <t>– High Punch</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Quick Upper Rush</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+          <t>Short Hammer Rush – High Punch</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-9 -2 -9</t>
+          <t>-13 -17</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>-2 +10 +2</t>
+          <t>-2 -5</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>JGc RC</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Will only juggles if the first hit connected as a counter hit.</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>4d52ef41-dcae-4fc4-bdcb-f8a463123b33</t>
+          <t>ed27d523-e067-478d-a635-03bda68904ba</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>cf23b4fe-0780-45f6-bc22-f43cfcbebd98</t>
+          <t>44d5340f-99e1-4aac-9e14-e98997b4543e</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>c5205cbe-a910-47e3-b327-6a7b4a7977cf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SS+2</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SS+2</t>
+          <t>DF+2,1,2,1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Megaton Breaker</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Megaton Breaker</t>
+          <t>Hammer Uppercut Rush</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-11 -6 -9 -1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +5 +3 +10</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>52</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10,15,12,15</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmmm</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmmm</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>8085378d-86c7-41a6-9504-9a757ef75411</t>
+          <t>eb0be9ab-e619-4f81-9092-4a7389c2ce1f</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>b6f87463-47da-4b12-9f14-d923dcce9717</t>
+          <t>9438c263-e8fc-4e2c-af89-31a54e2587cc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>b+2</t>
+          <t>Df+2,1,2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>b+2</t>
+          <t>Df+2,1,2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FC+DF+2,1,2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Piston Gun Assault</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Piston Gun Assault</t>
+          <t>Quick Upper Rush</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>-9 -2 -9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-2 +10 +2</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15,10,15</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JGc RC</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Will only juggles if the first hit connected as a counter hit.</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>9a4ed0b4-ba70-41ec-a123-5eddc4a7ab2a</t>
+          <t>4d52ef41-dcae-4fc4-bdcb-f8a463123b33</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>81291950-d59b-46af-ad22-122da97926bf</t>
+          <t>cf23b4fe-0780-45f6-bc22-f43cfcbebd98</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>b,db,d,DF+2</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Megaton Breaker</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Megaton Punch</t>
+          <t>Megaton Breaker</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8224,84 +8199,79 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>8e9ed1e9-0d4b-43ad-931e-7f6194c9b44d</t>
+          <t>8085378d-86c7-41a6-9504-9a757ef75411</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>a652d294-71e0-4bec-bb22-4689ee7e82c1</t>
+          <t>b6f87463-47da-4b12-9f14-d923dcce9717</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>df+2+3</t>
+          <t>b+2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>df+2+3</t>
+          <t>b+2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Low Ankle Swipe</t>
+          <t>Piston Gun Assault</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Low Ankle Swipe</t>
+          <t>Piston Gun Assault</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8326,64 +8296,64 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>49a6e8de-75b1-41d2-b384-921a77af43b1</t>
+          <t>9a4ed0b4-ba70-41ec-a123-5eddc4a7ab2a</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>256c09a8-bd31-44ad-ad05-68970c148b8c</t>
+          <t>81291950-d59b-46af-ad22-122da97926bf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DB+3,4,3,4,3,4</t>
+          <t>b,db,d,DF+2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cossack Kicks</t>
+          <t>Megaton Punch</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8398,109 +8368,114 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-20 -22 -20 -22...</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>-9 -11 -9 -11...</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>18,12,10,12,12,12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>LLLLLL</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>1115c571-df26-4a13-b659-eb3be2678c45</t>
+          <t>8e9ed1e9-0d4b-43ad-931e-7f6194c9b44d</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>065841ac-b63f-4297-bd7d-5a3d9988b5dd</t>
+          <t>a652d294-71e0-4bec-bb22-4689ee7e82c1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>df+2+3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>df+2+3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Digital Hans Headslide</t>
+          <t>Low Ankle Swipe</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Digital Hans Headslide</t>
+          <t>Low Ankle Swipe</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-110</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8525,288 +8500,323 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>(m_L)</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>(m_L)</t>
+          <t>L</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Hits mid at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>ee0c78c6-201c-4950-823b-d9ff59f28cf5</t>
+          <t>49a6e8de-75b1-41d2-b384-921a77af43b1</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>0faf1088-b25c-4572-b43d-e8af699f24b6</t>
+          <t>256c09a8-bd31-44ad-ad05-68970c148b8c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>DB+3,4,3,4,3,4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Cossack Kicks</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hip Press</t>
+          <t>Cossack Kicks</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-20 -22 -20 -22...</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-20 -22 -20 -22...</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>-9 -11 -9 -11...</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18,12,10,12,12,12</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18,12,10,12,12,12</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>LLLLLL</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>If the Hip Press whiffs the opponent, Gun Jack can chain into Sit Down extentions.</t>
+          <t>LLLLLL</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>4e6338f4-3c02-4262-9519-b405b222241f</t>
+          <t>1115c571-df26-4a13-b659-eb3be2678c45</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09e31194-c71f-483c-a454-ae43ac7426e8</t>
+          <t>065841ac-b63f-4297-bd7d-5a3d9988b5dd</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>d+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>d+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>Digital Hans Headslide</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sit Down</t>
+          <t>Digital Hans Headslide</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-110</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(m_L)</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>(m_L)</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hits mid at the start of the move or low at the end. It only hits once. Damage remains the same.</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
+          <t>ee0c78c6-201c-4950-823b-d9ff59f28cf5</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>3016fcba-a097-46bc-8637-75a688d08d25</t>
+          <t>0faf1088-b25c-4572-b43d-e8af699f24b6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>– ~3+4</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>d+3+4~3+4</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>– Hop Hip Press</t>
+          <t>Hip Press</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sit Down – Hop Hip Press</t>
+          <t>Hip Press</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-40</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-40</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-40</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>x -34</t>
+          <t>-40</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>-,35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -8816,7 +8826,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>-M</t>
+          <t>M</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -8826,39 +8836,39 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>ae3e53ab-3644-4aeb-a4ee-3e5aaac2dc7f</t>
+          <t>4e6338f4-3c02-4262-9519-b405b222241f</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>675e841f-1f01-42d9-a1f6-85e517b5bbb4</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
+          <t>09e31194-c71f-483c-a454-ae43ac7426e8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>– B</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>d+3+4,B</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>– Roll Back</t>
+          <t>Sit Down</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sit Down – Roll Back</t>
+          <t>Sit Down</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -8878,7 +8888,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -8888,84 +8898,114 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>25d0b1c8-be76-40d2-94b9-8b6ab9aff06d</t>
+          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>c6762a1e-a603-4ac5-8ec8-55e7fc50b79c</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
+          <t>3016fcba-a097-46bc-8637-75a688d08d25</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>– F</t>
+          <t>– ~3+4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>d+3+4,F</t>
+          <t>d+3+4~3+4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>– Roll Forward</t>
+          <t>– Hop Hip Press</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sit Down – Roll Forward</t>
+          <t>Sit Down – Hop Hip Press</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>-34</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>x -34</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>-,35</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>-M</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>If the Hip Press whiffs the opponent, Gun Jack can chain into Sit Down extentions.</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>f897a7f1-f113-40e7-af6d-66575cdff07d</t>
+          <t>ae3e53ab-3644-4aeb-a4ee-3e5aaac2dc7f</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>d833031b-9852-4d1f-bdf7-6f0b87588f26</t>
+          <t>675e841f-1f01-42d9-a1f6-85e517b5bbb4</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -8977,92 +9017,62 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>– 1,2,1,2</t>
+          <t>– B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>d+3+4,1,2,1,2</t>
+          <t>d+3+4,B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>– Sitting Punches</t>
+          <t>– Roll Back</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sit Down – Sitting Punches</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-45 -43 -45 -43</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>-35 -32 -35 -32</t>
+          <t>Sit Down – Roll Back</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>x -35 -32 -35 -32</t>
+          <t>x</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>10,10,10,10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>-,10,10,10,10</t>
+          <t>-,-</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>llll</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>-llll</t>
+          <t>--</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>a3493e9e-ed4b-4f9c-837d-e923d43f8323</t>
+          <t>25d0b1c8-be76-40d2-94b9-8b6ab9aff06d</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>92173c28-7d22-4710-81d3-65f7fe6ff406</t>
+          <t>c6762a1e-a603-4ac5-8ec8-55e7fc50b79c</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -9074,97 +9084,67 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>– F</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KND d+1+2</t>
+          <t>d+3+4,F</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down</t>
+          <t>– Roll Forward</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>+11</t>
+          <t>Sit Down – Roll Forward</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>x</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-,-</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>--</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>11ec1118-3651-4e77-967a-38f94c577687</t>
+          <t>f897a7f1-f113-40e7-af6d-66575cdff07d</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>871e0600-4ee2-42d9-92aa-41d7019b8e21</t>
+          <t>d833031b-9852-4d1f-bdf7-6f0b87588f26</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9156,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KND d+1+2,1,2,1,2</t>
+          <t>d+3+4,1,2,1,2</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9186,7 +9166,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Spring Hammer - Sit Down – Sitting Punches</t>
+          <t>Sit Down – Sitting Punches</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9194,11 +9174,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>-45 -43 -45 -43</t>
@@ -9206,7 +9181,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>+7 -45 -43 -45 -43</t>
+          <t>-45 -43 -45 -43</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9216,7 +9191,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>+11 -35 -32 -35 -32</t>
+          <t>-35 -32 -35 -32</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -9226,7 +9201,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>+11 -35 -32 -35 -32</t>
+          <t>x -35 -32 -35 -32</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9241,7 +9216,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>12,10,10,10,10</t>
+          <t>-,10,10,10,10</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9251,440 +9226,460 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>mllll</t>
+          <t>-llll</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>b59464f2-5946-4444-bbbc-6337a84aca7e</t>
+          <t>a3493e9e-ed4b-4f9c-837d-e923d43f8323</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>0ea9598e-6398-4ca9-a4e5-0a24d08cb813</t>
+          <t>92173c28-7d22-4710-81d3-65f7fe6ff406</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>11ec1118-3651-4e77-967a-38f94c577687</t>
+          <t>8f43a843-cb1c-4575-951e-2f6efcb3bb45</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>KND d+1+2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KND d+1+2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>11ec1118-3651-4e77-967a-38f94c577687</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>871e0600-4ee2-42d9-92aa-41d7019b8e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KND d+1+2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>– Sitting Punches</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Spring Hammer - Sit Down – Sitting Punches</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>+7 -45 -43 -45 -43</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>+11 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>-35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>+11 -35 -32 -35 -32</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>10,10,10,10</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>12,10,10,10,10</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>llll</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>mllll</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>b59464f2-5946-4444-bbbc-6337a84aca7e</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>0ea9598e-6398-4ca9-a4e5-0a24d08cb813</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>11ec1118-3651-4e77-967a-38f94c577687</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>d+4</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>d+4</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Ganny Stomp</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Ganny Stomp</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>55fc7105-30fe-4109-8ee8-a62c7a9d0729</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>697a4c6c-59d7-49cf-9db3-51fc801ccc3d</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>Unblockable Arts</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
+      <c r="B107" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D105" s="1" t="inlineStr">
+      <c r="D107" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E105" s="1" t="inlineStr">
+      <c r="E107" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="F107" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
+      <c r="G107" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H105" s="1" t="inlineStr">
+      <c r="H107" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I105" s="1" t="inlineStr">
+      <c r="I107" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J105" s="1" t="inlineStr">
+      <c r="J107" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K105" s="1" t="inlineStr">
+      <c r="K107" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L105" s="1" t="inlineStr">
+      <c r="L107" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M105" s="1" t="inlineStr">
+      <c r="M107" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N105" s="1" t="inlineStr">
+      <c r="N107" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O105" s="1" t="inlineStr">
+      <c r="O107" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P105" s="1" t="inlineStr">
+      <c r="P107" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q105" s="1" t="inlineStr">
+      <c r="Q107" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R105" s="1" t="inlineStr">
+      <c r="R107" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S105" s="1" t="inlineStr">
+      <c r="S107" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T105" s="1" t="inlineStr">
+      <c r="T107" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U105" s="1" t="inlineStr">
+      <c r="U107" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V105" s="1" t="inlineStr">
+      <c r="V107" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W105" s="1" t="inlineStr">
+      <c r="W107" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X105" s="1" t="inlineStr">
+      <c r="X107" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y105" s="1" t="inlineStr">
+      <c r="Y107" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z105" s="1" t="inlineStr">
+      <c r="Z107" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA105" s="1" t="inlineStr">
+      <c r="AA107" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB105" s="1" t="inlineStr">
+      <c r="AB107" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>f+4~1</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>f+4~1</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Dark Greeting</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Dark Greeting</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>!</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>e8983d06-9202-416e-9693-52a1ba37f79a</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>2d81b35f-0925-4146-90f5-ba2dedf33d01</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>3+4</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>3+4</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Gigaton Stomp</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Gigaton Stomp</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>[!]</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>[!]</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>355df573-dd5b-4e9a-a5e2-65f9c2ffcca8</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>d64a730c-f2ef-4dc9-b8ac-7b62deb76486</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3+4,3+4</t>
+          <t>f+4~1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3+4,3+4</t>
+          <t>f+4~1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Double Thrust Gigaton Stomp</t>
+          <t>Dark Greeting</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Double Thrust Gigaton Stomp</t>
+          <t>Dark Greeting</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9709,69 +9704,74 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>101</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>101</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>9e078495-5321-4990-aab6-cf083622c5ab</t>
+          <t>e8983d06-9202-416e-9693-52a1ba37f79a</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>cdcf1f3c-2f6a-4074-88bb-b2fd601e3a4d</t>
+          <t>2d81b35f-0925-4146-90f5-ba2dedf33d01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3+4,3+4,3+4</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3+4,3+4,3+4</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Triple Thrust Gigaton Stomp</t>
+          <t>Gigaton Stomp</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Triple Thrust Gigaton Stomp</t>
+          <t>Gigaton Stomp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9796,17 +9796,17 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -9821,509 +9821,589 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>e83fa056-6a98-430a-99bd-803d6fa65591</t>
+          <t>355df573-dd5b-4e9a-a5e2-65f9c2ffcca8</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>cbb272da-77d3-4584-93f8-ca6d85db2f33</t>
+          <t>d64a730c-f2ef-4dc9-b8ac-7b62deb76486</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>3+4,3+4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>hcf</t>
+          <t>3+4,3+4</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>Double Thrust Gigaton Stomp</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gigaton Start Up</t>
+          <t>Double Thrust Gigaton Stomp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[!]</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[!]</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>873d17ea-6b9b-42f4-af13-9ae5ca9cf718</t>
+          <t>9e078495-5321-4990-aab6-cf083622c5ab</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>aad579aa-9c5f-4411-a135-edffbbd50d26</t>
+          <t>cdcf1f3c-2f6a-4074-88bb-b2fd601e3a4d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>– b,db,d,df,f,uf,u,ub</t>
+          <t>3+4,3+4,3+4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+          <t>3+4,3+4,3+4</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>– Wind Up</t>
+          <t>Triple Thrust Gigaton Stomp</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gigaton Start Up – Wind Up</t>
+          <t>Triple Thrust Gigaton Stomp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>-,-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>[!]</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Can be repeated up to 5 times.</t>
+          <t>[!]</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>70729f45-0998-4391-809f-5cb720510443</t>
+          <t>e83fa056-6a98-430a-99bd-803d6fa65591</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>bd10840b-d8d7-46c1-9119-1be547e12083</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>873d17ea-6b9b-42f4-af13-9ae5ca9cf718</t>
+          <t>cbb272da-77d3-4584-93f8-ca6d85db2f33</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>hcf</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>873d17ea-6b9b-42f4-af13-9ae5ca9cf718</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>aad579aa-9c5f-4411-a135-edffbbd50d26</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>– b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>hcf,b,db,d,df,f,uf,u,ub</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>– Wind Up</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Gigaton Start Up – Wind Up</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>-,-</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Can be repeated up to 5 times.</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>70729f45-0998-4391-809f-5cb720510443</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>bd10840b-d8d7-46c1-9119-1be547e12083</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>873d17ea-6b9b-42f4-af13-9ae5ca9cf718</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>–– 1</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>hcf,b,db,d,df,f,uf,u,ub,1</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>–– Gigaton Punch</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>Gigaton Start Up – Wind Up – Gigaton Punch</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>-,-,40</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="R114" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>--!</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr">
+      <c r="W114" t="inlineStr">
         <is>
           <t>Damage increases to 60, 80 and 199 with each extra Wind Up. Becomes Unblockable after 2 Wind Ups.</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>3068c791-feb4-4b64-acdf-cbc26e7505ee</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>1fb4c842-1743-4a9d-ac54-14ddd794cd29</t>
         </is>
       </c>
-      <c r="AA112" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>70729f45-0998-4391-809f-5cb720510443</t>
         </is>
       </c>
     </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr">
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>String Hit Arts</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
+      <c r="B117" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D115" s="1" t="inlineStr">
+      <c r="D117" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E115" s="1" t="inlineStr">
+      <c r="E117" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F115" s="1" t="inlineStr">
+      <c r="F117" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G115" s="1" t="inlineStr">
+      <c r="G117" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H115" s="1" t="inlineStr">
+      <c r="H117" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I115" s="1" t="inlineStr">
+      <c r="I117" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J115" s="1" t="inlineStr">
+      <c r="J117" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K115" s="1" t="inlineStr">
+      <c r="K117" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L115" s="1" t="inlineStr">
+      <c r="L117" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M115" s="1" t="inlineStr">
+      <c r="M117" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N115" s="1" t="inlineStr">
+      <c r="N117" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O115" s="1" t="inlineStr">
+      <c r="O117" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P115" s="1" t="inlineStr">
+      <c r="P117" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q115" s="1" t="inlineStr">
+      <c r="Q117" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R115" s="1" t="inlineStr">
+      <c r="R117" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S115" s="1" t="inlineStr">
+      <c r="S117" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T115" s="1" t="inlineStr">
+      <c r="T117" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U115" s="1" t="inlineStr">
+      <c r="U117" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V115" s="1" t="inlineStr">
+      <c r="V117" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W115" s="1" t="inlineStr">
+      <c r="W117" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X115" s="1" t="inlineStr">
+      <c r="X117" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y115" s="1" t="inlineStr">
+      <c r="Y117" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z115" s="1" t="inlineStr">
+      <c r="Z117" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA115" s="1" t="inlineStr">
+      <c r="AA117" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB115" s="1" t="inlineStr">
+      <c r="AB117" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,11+2,1+2</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,2,1,2,11+2,1+2</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,21,25</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>sLLmmmmmmm</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,21,2,1,d+1+2,1+2</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>D+2,1,1,1,21,2,1,d+1+2,1+2</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>10,6,5,7,7,6,6,8,12,35</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>sLLmmmmmlm</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>ML only</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+          <t>D+2,1,1,1,2,1,2,11+2,1+2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+          <t>D+2,1,1,1,2,1,2,11+2,1+2</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>15,8,5,5,5,8,6,8,21,25</t>
+          <t>10,6,5,7,7,6,6,8,21,25</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>hmLLLmmmmm</t>
+          <t>sLLmmmmmmm</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
@@ -10335,45 +10415,139 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>D+2,1,1,1,21,2,1,d+1+2,1+2</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D+2,1,1,1,21,2,1,d+1+2,1+2</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>10,6,5,7,7,6,6,8,12,35</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>sLLmmmmmlm</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>uf+1,1,4,3,4,1,2,1,1+2,1+2</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>15,8,5,5,5,8,6,8,21,25</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>hmLLLmmmmm</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>uf+1,1,4,3,4,12,1,d+1+2,1+2</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>15,8,5,5,5,8,6,8,12,35</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R121" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
+      <c r="AB121" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/gunjack_step8.xlsx
+++ b/sources/gunjack_step8.xlsx
@@ -9811,12 +9811,12 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -9985,12 +9985,12 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">

--- a/sources/gunjack_step8.xlsx
+++ b/sources/gunjack_step8.xlsx
@@ -1484,6 +1484,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
@@ -1546,6 +1551,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
@@ -1618,6 +1628,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
@@ -1680,6 +1695,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
@@ -1742,6 +1762,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
           <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
@@ -1797,6 +1822,11 @@
       <c r="U20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>251f1e2f-c3c7-4333-a3d4-49d19c52d36c</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -10401,6 +10431,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
+        </is>
+      </c>
       <c r="Z118" t="inlineStr">
         <is>
           <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
@@ -10448,6 +10483,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
       <c r="Z119" t="inlineStr">
         <is>
           <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
@@ -10495,6 +10535,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
       <c r="Z120" t="inlineStr">
         <is>
           <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
@@ -10540,6 +10585,11 @@
       <c r="S121" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
